--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Tips.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Tips.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8200"/>
+    <workbookView windowWidth="25600" windowHeight="10480"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -87,19 +87,19 @@
     <t>切换阶段失败提示_标题</t>
   </si>
   <si>
-    <t>PhaseSwitch_Blocked_Title</t>
-  </si>
-  <si>
-    <t>Tips.PhaseSwitch.Blocked.Title</t>
+    <t>Tips_PhaseSwitchBlocked_Title</t>
+  </si>
+  <si>
+    <t>Tips.PhaseSwitchBlocked.Title</t>
   </si>
   <si>
     <t>切换阶段失败提示_内容</t>
   </si>
   <si>
-    <t>PhaseSwitch_Blocked_Content</t>
-  </si>
-  <si>
-    <t>Tips.PhaseSwitch.Blocked.Content</t>
+    <t>Tips_PhaseSwitchBlocked_Content</t>
+  </si>
+  <si>
+    <t>Tips.PhaseSwitchBlocked.Content</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1116,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1" spans="2:5">
+    <row r="5" ht="32" customHeight="1" spans="1:5">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="2:5">
+    <row r="6" ht="28" customHeight="1" spans="1:5">
       <c r="B6" s="1">
         <v>2</v>
       </c>

--- a/AAAGameData/DataTables/Text/LocalizationTextTable_Tips.xlsx
+++ b/AAAGameData/DataTables/Text/LocalizationTextTable_Tips.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>#</t>
   </si>
@@ -100,6 +100,33 @@
   </si>
   <si>
     <t>Tips.PhaseSwitchBlocked.Content</t>
+  </si>
+  <si>
+    <t>卡牌打出失败提示_标题</t>
+  </si>
+  <si>
+    <t>Tips_CardPlayBlocked_Title</t>
+  </si>
+  <si>
+    <t>Tips.CardPlayBlocked.Title</t>
+  </si>
+  <si>
+    <t>卡牌打出失败提示_禁止区域</t>
+  </si>
+  <si>
+    <t>Tips_CardPlayBlocked_ForbiddenArea</t>
+  </si>
+  <si>
+    <t>Tips.CardPlayBlocked.ForbiddenArea</t>
+  </si>
+  <si>
+    <t>卡牌打出失败提示_人口不足</t>
+  </si>
+  <si>
+    <t>Tips_CardPlayBlocked_InsufficientSupply</t>
+  </si>
+  <si>
+    <t>Tips.CardPlayBlocked.InsufficientSupply</t>
   </si>
 </sst>
 </file>
@@ -1052,8 +1079,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.75" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="2.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.5833333333333" style="1" customWidth="1"/>
@@ -1144,6 +1171,48 @@
         <v>17</v>
       </c>
     </row>
+    <row r="7" ht="28.75" spans="1:5">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="28.75" spans="1:5">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" ht="28.75" spans="1:5">
+      <c r="B9" s="1">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
